--- a/解题-gpt/结果/问题三_中继部署方案_修复版.xlsx
+++ b/解题-gpt/结果/问题三_中继部署方案_修复版.xlsx
@@ -82,16 +82,16 @@
     <t>RE-01,RE-02</t>
   </si>
   <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295948, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295948, "end_min": 213.98774278104838, "energy_kwh": 1.3021282277316297}, {"component_id": "RE-02", "phase": "return", "start_min": 213.98774278104835, "end_min": 222.81127487594068, "energy_kwh": 0.07328436515210275}]</t>
-  </si>
-  <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 189.5492509213889, "energy_kwh": 0.856240995935087}, {"component_id": "RE-02", "phase": "return", "start_min": 189.5492509213889, "end_min": 200.95492577293726, "energy_kwh": 0.12277543465467701}]</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.96256672295948, 172.96256672295948], "RE-02": [222.81127487594068, 252.81127487594068]}</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [200.95492577293726, 230.95492577293726]}</t>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295945, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295945, "end_min": 182.2643138933139, "energy_kwh": 0.7205320314564982}, {"component_id": "RE-02", "phase": "return", "start_min": 182.2643138933139, "end_min": 191.08784598820623, "energy_kwh": 0.07328436515210275}]</t>
+  </si>
+  <si>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 182.02506583457242, "energy_kwh": 0.7182976026767847}, {"component_id": "RE-02", "phase": "return", "start_min": 182.02506583457242, "end_min": 193.43074068612077, "energy_kwh": 0.12277543465467701}]</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.96256672295945, 172.96256672295945], "RE-02": [191.08784598820623, 221.08784598820623]}</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [193.43074068612077, 223.43074068612077]}</t>
   </si>
 </sst>
 </file>
@@ -525,25 +525,25 @@
         <v>7.323532094892318</v>
       </c>
       <c r="G2">
-        <v>213.9877427810484</v>
+        <v>182.2643138933139</v>
       </c>
       <c r="H2">
-        <v>222.8112748759407</v>
+        <v>191.0878459882062</v>
       </c>
       <c r="I2">
-        <v>205.6147938843214</v>
+        <v>173.6387822549022</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2">
-        <v>3.935412592883733</v>
+        <v>3.353816396608601</v>
       </c>
       <c r="L2">
         <v>0.1465687303042055</v>
       </c>
       <c r="M2">
-        <v>3.788843862579527</v>
+        <v>3.207247666304396</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -578,25 +578,25 @@
         <v>9.905674851548365</v>
       </c>
       <c r="G3">
-        <v>189.5492509213889</v>
+        <v>182.0250658345724</v>
       </c>
       <c r="H3">
-        <v>200.9549257729373</v>
+        <v>193.4307406861208</v>
       </c>
       <c r="I3">
-        <v>205.6147938843214</v>
+        <v>173.6387822549022</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3">
-        <v>3.539016430589764</v>
+        <v>3.401073037331462</v>
       </c>
       <c r="L3">
         <v>0.245550869309354</v>
       </c>
       <c r="M3">
-        <v>3.29346556128041</v>
+        <v>3.155522168022108</v>
       </c>
       <c r="N3">
         <v>2</v>

--- a/解题-gpt/结果/问题三_中继部署方案_修复版.xlsx
+++ b/解题-gpt/结果/问题三_中继部署方案_修复版.xlsx
@@ -82,16 +82,16 @@
     <t>RE-01,RE-02</t>
   </si>
   <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295945, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295945, "end_min": 182.2643138933139, "energy_kwh": 0.7205320314564982}, {"component_id": "RE-02", "phase": "return", "start_min": 182.2643138933139, "end_min": 191.08784598820623, "energy_kwh": 0.07328436515210275}]</t>
-  </si>
-  <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 182.02506583457242, "energy_kwh": 0.7182976026767847}, {"component_id": "RE-02", "phase": "return", "start_min": 182.02506583457242, "end_min": 193.43074068612077, "energy_kwh": 0.12277543465467701}]</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.96256672295945, 172.96256672295945], "RE-02": [191.08784598820623, 221.08784598820623]}</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [193.43074068612077, 223.43074068612077]}</t>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295945, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295945, "end_min": 180.35166741501502, "energy_kwh": 0.6854668460210185}, {"component_id": "RE-02", "phase": "return", "start_min": 180.351667415015, "end_min": 189.17519950990732, "energy_kwh": 0.07328436515210275}]</t>
+  </si>
+  <si>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 165.12575842172168, "energy_kwh": 0.40847696677452117}, {"component_id": "RE-02", "phase": "return", "start_min": 165.12575842172168, "end_min": 176.53143327327004, "energy_kwh": 0.12277543465467701}]</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.96256672295945, 172.96256672295945], "RE-02": [189.17519950990732, 219.17519950990732]}</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [176.53143327327004, 206.53143327327004]}</t>
   </si>
 </sst>
 </file>
@@ -525,25 +525,25 @@
         <v>7.323532094892318</v>
       </c>
       <c r="G2">
-        <v>182.2643138933139</v>
+        <v>180.351667415015</v>
       </c>
       <c r="H2">
-        <v>191.0878459882062</v>
+        <v>189.1751995099073</v>
       </c>
       <c r="I2">
-        <v>173.6387822549022</v>
+        <v>171.5840041697735</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2">
-        <v>3.353816396608601</v>
+        <v>3.318751211173121</v>
       </c>
       <c r="L2">
         <v>0.1465687303042055</v>
       </c>
       <c r="M2">
-        <v>3.207247666304396</v>
+        <v>3.172182480868916</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -578,25 +578,25 @@
         <v>9.905674851548365</v>
       </c>
       <c r="G3">
-        <v>182.0250658345724</v>
+        <v>165.1257584217217</v>
       </c>
       <c r="H3">
-        <v>193.4307406861208</v>
+        <v>176.53143327327</v>
       </c>
       <c r="I3">
-        <v>173.6387822549022</v>
+        <v>171.5840041697735</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3">
-        <v>3.401073037331462</v>
+        <v>3.091252401429199</v>
       </c>
       <c r="L3">
         <v>0.245550869309354</v>
       </c>
       <c r="M3">
-        <v>3.155522168022108</v>
+        <v>2.845701532119845</v>
       </c>
       <c r="N3">
         <v>2</v>
